--- a/verification/cases/roundtrip/with_table/init.xlsx
+++ b/verification/cases/roundtrip/with_table/init.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{367ED463-D7A0-440A-9B56-1C6979854222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="75" windowWidth="19020" windowHeight="8580"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -27,8 +33,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,28 +67,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabella1" displayName="Tabella1" ref="A1:B2" totalsRowShown="0">
-  <autoFilter ref="A1:B2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabella1" displayName="Tabella1" ref="A1:B2" totalsRowShown="0">
+  <autoFilter ref="A1:B2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="a"/>
-    <tableColumn id="2" name="b"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="a"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="b"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -120,7 +134,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -154,6 +168,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -188,9 +203,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -363,11 +379,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -375,7 +391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -393,18 +409,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
